--- a/output/pdf_financials_xlsx/YEG.xlsx
+++ b/output/pdf_financials_xlsx/YEG.xlsx
@@ -6560,7 +6560,11 @@
           <t>Prepaids and deposits (Note 10)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -9664,7 +9668,11 @@
           <t>Prepaids and deposits (Note 8)</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -10462,7 +10470,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/YEG.xlsx
+++ b/output/pdf_financials_xlsx/YEG.xlsx
@@ -773,13 +773,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>0.202003</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.126543</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>0.049768</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0.537045</v>
@@ -812,13 +812,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-0.202003</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>-0.126543</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
+        <v>-0.049768</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>0.001291</v>
@@ -875,13 +875,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.037108</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.018241</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.013667</v>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
@@ -1508,13 +1508,13 @@
         <v>-1.21905</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.06944500000000001</v>
+        <v>0.032337</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>4.161533</v>
+        <v>4.143292</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>7.810055</v>
+        <v>7.796388</v>
       </c>
       <c r="K27" s="1" t="inlineStr">
         <is>
@@ -1586,13 +1586,13 @@
         <v>-1.216688</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.07294399999999999</v>
+        <v>0.035836</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>4.166044</v>
+        <v>4.147803</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>7.828298</v>
+        <v>7.814631</v>
       </c>
       <c r="K29" s="1" t="inlineStr">
         <is>
@@ -1762,19 +1762,19 @@
         <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.365923</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.344837</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.039489</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.001763</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>2.180351</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>2.950636</v>
@@ -1836,19 +1836,19 @@
         <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.365923</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.344837</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.039489</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.001763</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>2.180351</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>2.950636</v>
@@ -2280,19 +2280,19 @@
         <v>0.51429</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.365923</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.344837</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.054661</v>
+        <v>0.015172</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.371423</v>
+        <v>0.36966</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>3.22942</v>
+        <v>1.049069</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.483131</v>
@@ -10204,7 +10204,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -11204,7 +11204,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -11798,7 +11798,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -20070,7 +20070,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -24036,7 +24036,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E285" s="5" t="n">

--- a/output/pdf_financials_xlsx/YEG.xlsx
+++ b/output/pdf_financials_xlsx/YEG.xlsx
@@ -1061,13 +1061,13 @@
         <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.095373</v>
+        <v>-0.236181</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>0.042495</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.04533</v>
+        <v>-0.007854</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>0.231418</v>
@@ -1669,13 +1669,13 @@
         <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-341.2027761877504</v>
+        <v>-844.9520606754437</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-2.636120464408807</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-3.718469299864649</v>
+        <v>-0.6442721791559001</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>333.2392540859673</v>
@@ -3030,16 +3030,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.084205</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.135292</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.183861</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.175536</v>
       </c>
     </row>
     <row r="68">
@@ -4209,10 +4209,8 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.202003</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-0.101543</v>
@@ -4250,10 +4248,8 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
         <v>0</v>
@@ -4289,10 +4285,8 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>-0.025</v>
@@ -4328,10 +4322,8 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C102" s="3" t="n">
         <v>0</v>
@@ -4367,10 +4359,8 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C103" s="3" t="n">
         <v>0</v>
@@ -4406,10 +4396,8 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0.03975</v>
       </c>
       <c r="C104" s="3" t="n">
         <v>-0.021824</v>
@@ -4445,10 +4433,8 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C105" s="3" t="n">
         <v>0</v>
@@ -4484,10 +4470,8 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.03975</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>-0.046824</v>
@@ -4496,25 +4480,25 @@
         <v>0.028682</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.002608</v>
+        <v>0.016709</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>-0.216706</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0</v>
+        <v>-0.341703</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0</v>
+        <v>-0.07623000000000001</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0</v>
+        <v>0.611172</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0</v>
+        <v>-0.122454</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0</v>
+        <v>0.216663</v>
       </c>
     </row>
     <row r="107">
@@ -4523,10 +4507,8 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0.088659</v>
       </c>
       <c r="C107" s="3" t="n">
         <v>0</v>
@@ -4562,10 +4544,8 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C108" s="3" t="n">
         <v>0</v>
@@ -4601,10 +4581,8 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C109" s="3" t="n">
         <v>0</v>
@@ -4640,10 +4618,8 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
         <v>0</v>
@@ -4679,10 +4655,8 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -4700,13 +4674,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.005381</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="K111" s="3" t="n">
         <v>0</v>
@@ -4718,10 +4692,8 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
@@ -4757,10 +4729,8 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C113" s="3" t="n">
         <v>0</v>
@@ -4796,10 +4766,8 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>0</v>
@@ -4835,10 +4803,8 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -4874,10 +4840,8 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
         <v>0</v>
@@ -4898,13 +4862,13 @@
         <v>0</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-0.051367</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-0.020364</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-0.022768</v>
       </c>
     </row>
     <row r="117">
@@ -4913,10 +4877,8 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C117" s="3" t="n">
         <v>0</v>
@@ -4952,10 +4914,8 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>0</v>
@@ -4991,10 +4951,8 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
@@ -5034,10 +4992,8 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>0</v>
@@ -5073,10 +5029,8 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>0</v>
@@ -5112,10 +5066,8 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C122" s="3" t="n">
         <v>0</v>
@@ -5151,10 +5103,8 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C123" s="3" t="n">
         <v>0</v>
@@ -5190,10 +5140,8 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>0</v>
@@ -5229,10 +5177,8 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0</v>
@@ -5268,10 +5214,8 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C126" s="3" t="n">
         <v>0</v>
@@ -5364,10 +5308,8 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0.587884</v>
       </c>
       <c r="C128" s="3" t="n">
         <v>0</v>
@@ -5403,10 +5345,8 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>0.587884</v>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
@@ -5489,10 +5429,8 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C131" s="3" t="n">
         <v>0</v>
@@ -5528,10 +5466,8 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>0.51429</v>
       </c>
       <c r="C132" s="3" t="n">
         <v>-0.148367</v>
@@ -5610,10 +5546,8 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -5631,13 +5565,13 @@
         <v>0</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005381</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="K134" s="3" t="n">
         <v>0</v>
@@ -5649,10 +5583,8 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-0.07359400000000001</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.148367</v>
@@ -5670,13 +5602,13 @@
         <v>-0.976475</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>0.781186</v>
+        <v>0.775805</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>3.630554</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>4.827999</v>
+        <v>4.817999</v>
       </c>
       <c r="K135" s="3" t="n">
         <v>5.131572</v>
@@ -5693,7 +5625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N308"/>
+  <dimension ref="A1:N316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13122,7 +13054,11 @@
           <t>Deferred income tax expense (Note 16)</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -13608,7 +13544,11 @@
           <t>Change in non-cash operating working capital (Note 18(a))</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -14434,7 +14374,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -14498,7 +14442,11 @@
           <t>Acquisition of intangible asset</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -15190,7 +15138,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -16523,10 +16475,8 @@
           <t>FinancingCashFlow</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E169" s="5" t="n">
+        <v>0.587884</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17172,7 +17122,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -17236,7 +17190,11 @@
           <t>Change in non-cash operating working capital (Note 18)</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -18288,7 +18246,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -18416,7 +18378,11 @@
           <t>Change in non-cash operating working capital (Note 15)</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -18548,7 +18514,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -19517,20 +19487,26 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Operating Activities</t>
+        </is>
+      </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Rental revenue (Note 13) $</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E215" s="5" t="n">
+        <v>-0.202003</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19547,20 +19523,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I215" s="5" t="n">
-        <v>0.48477</v>
-      </c>
-      <c r="J215" s="5" t="n">
-        <v>1.076916</v>
-      </c>
-      <c r="K215" s="5" t="n">
-        <v>2.993334</v>
-      </c>
-      <c r="L215" s="5" t="n">
-        <v>7.196467</v>
-      </c>
-      <c r="M215" s="5" t="n">
-        <v>9.847436</v>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N215" t="inlineStr">
         <is>
@@ -19571,20 +19557,26 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Operating Activities</t>
+        </is>
+      </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Direct operating costs (Note 14)</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr"/>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share-based compensation (Note 6)</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E216" s="5" t="n">
+        <v>0.088659</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19616,11 +19608,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L216" s="5" t="n">
-        <v>-2.91563</v>
-      </c>
-      <c r="M216" s="5" t="n">
-        <v>-4.07416</v>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N216" t="inlineStr">
         <is>
@@ -19631,20 +19627,26 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Add back items not involving cash</t>
+        </is>
+      </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Net rental income</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr"/>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E217" s="5" t="n">
+        <v>0.03975</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19661,20 +19663,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I217" s="5" t="n">
-        <v>0.443597</v>
-      </c>
-      <c r="J217" s="5" t="n">
-        <v>0.560704</v>
-      </c>
-      <c r="K217" s="5" t="n">
-        <v>1.845211</v>
-      </c>
-      <c r="L217" s="5" t="n">
-        <v>4.280837</v>
-      </c>
-      <c r="M217" s="5" t="n">
-        <v>5.773276</v>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N217" t="inlineStr">
         <is>
@@ -19685,24 +19697,26 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Add back items not involving cash</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Financing costs (Note 15)</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr"/>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash used in operating activities $</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E218" s="5" t="n">
+        <v>-0.07359400000000001</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19719,20 +19733,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I218" s="5" t="n">
-        <v>0.092403</v>
-      </c>
-      <c r="J218" s="5" t="n">
-        <v>0.479372</v>
-      </c>
-      <c r="K218" s="5" t="n">
-        <v>1.576049</v>
-      </c>
-      <c r="L218" s="5" t="n">
-        <v>3.446952</v>
-      </c>
-      <c r="M218" s="5" t="n">
-        <v>4.896239</v>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N218" t="inlineStr">
         <is>
@@ -19743,28 +19767,26 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>General and administration (Note 14)</t>
+          <t>Issuance of common shares, net of share issuance costs (Note 6) $</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E219" s="5" t="n">
+        <v>0.587884</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19781,20 +19803,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I219" s="5" t="n">
-        <v>0.129356</v>
-      </c>
-      <c r="J219" s="5" t="n">
-        <v>0.946261</v>
-      </c>
-      <c r="K219" s="5" t="n">
-        <v>0.7241030000000001</v>
-      </c>
-      <c r="L219" s="5" t="n">
-        <v>0.847383</v>
-      </c>
-      <c r="M219" s="5" t="n">
-        <v>1.009775</v>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N219" t="inlineStr">
         <is>
@@ -19805,28 +19837,22 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Depreciation and amortization</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Increase in cash resources $</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" s="5" t="n">
+        <v>0.51429</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19853,14 +19879,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K220" s="5" t="n">
-        <v>0.003499</v>
-      </c>
-      <c r="L220" s="5" t="n">
-        <v>0.004511</v>
-      </c>
-      <c r="M220" s="5" t="n">
-        <v>0.018243</v>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N220" t="inlineStr">
         <is>
@@ -19871,24 +19903,20 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Cash resources, beginning of period</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -19904,23 +19932,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H221" s="5" t="n">
-        <v>0.537045</v>
-      </c>
-      <c r="I221" s="5" t="n">
-        <v>0.390527</v>
-      </c>
-      <c r="J221" s="5" t="n">
-        <v>1.565153</v>
-      </c>
-      <c r="K221" s="5" t="n">
-        <v>2.447864</v>
-      </c>
-      <c r="L221" s="5" t="n">
-        <v>4.298846</v>
-      </c>
-      <c r="M221" s="5" t="n">
-        <v>5.924257</v>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N221" t="inlineStr">
         <is>
@@ -19931,28 +19971,22 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Loss before other income</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash resources, end of period $</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" s="5" t="n">
+        <v>0.51429</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19974,17 +20008,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J222" s="5" t="n">
-        <v>-1.004449</v>
-      </c>
-      <c r="K222" s="5" t="n">
-        <v>-0.602653</v>
-      </c>
-      <c r="L222" s="5" t="n">
-        <v>-0.018009</v>
-      </c>
-      <c r="M222" s="5" t="n">
-        <v>-0.150981</v>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N222" t="inlineStr">
         <is>
@@ -19998,14 +20040,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Other income</t>
-        </is>
-      </c>
+      <c r="B223" t="inlineStr"/>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Fair value adjustment on investment properties (Note 4)</t>
+          <t>Rental revenue (Note 13) $</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
@@ -20029,22 +20067,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I223" s="5" t="n">
+        <v>0.48477</v>
       </c>
       <c r="J223" s="5" t="n">
-        <v>0.573039</v>
+        <v>1.076916</v>
       </c>
       <c r="K223" s="5" t="n">
-        <v>0.6349900000000001</v>
+        <v>2.993334</v>
       </c>
       <c r="L223" s="5" t="n">
-        <v>4.161301</v>
+        <v>7.196467</v>
       </c>
       <c r="M223" s="5" t="n">
-        <v>7.947369</v>
+        <v>9.847436</v>
       </c>
       <c r="N223" t="inlineStr">
         <is>
@@ -20058,21 +20094,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Other income</t>
-        </is>
-      </c>
+      <c r="B224" t="inlineStr"/>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Direct operating costs (Note 14)</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -20103,14 +20131,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K224" s="5" t="n">
-        <v>0.037108</v>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L224" s="5" t="n">
-        <v>0.018241</v>
+        <v>-2.91563</v>
       </c>
       <c r="M224" s="5" t="n">
-        <v>0.013667</v>
+        <v>-4.07416</v>
       </c>
       <c r="N224" t="inlineStr">
         <is>
@@ -20124,21 +20154,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Other income</t>
-        </is>
-      </c>
+      <c r="B225" t="inlineStr"/>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Income before income taxes</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Net rental income</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -20159,24 +20181,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I225" s="5" t="n">
+        <v>0.443597</v>
+      </c>
+      <c r="J225" s="5" t="n">
+        <v>0.560704</v>
       </c>
       <c r="K225" s="5" t="n">
-        <v>0.06944500000000001</v>
+        <v>1.845211</v>
       </c>
       <c r="L225" s="5" t="n">
-        <v>4.161533</v>
+        <v>4.280837</v>
       </c>
       <c r="M225" s="5" t="n">
-        <v>7.810055</v>
+        <v>5.773276</v>
       </c>
       <c r="N225" t="inlineStr">
         <is>
@@ -20192,19 +20210,15 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Deferred income tax expense (Note 16)</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Financing costs (Note 15)</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -20225,24 +20239,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I226" s="5" t="n">
+        <v>0.092403</v>
+      </c>
+      <c r="J226" s="5" t="n">
+        <v>0.479372</v>
       </c>
       <c r="K226" s="5" t="n">
-        <v>-0.231418</v>
+        <v>1.576049</v>
       </c>
       <c r="L226" s="5" t="n">
-        <v>-0.723573</v>
+        <v>3.446952</v>
       </c>
       <c r="M226" s="5" t="n">
-        <v>-1.242774</v>
+        <v>4.896239</v>
       </c>
       <c r="N226" t="inlineStr">
         <is>
@@ -20258,17 +20268,17 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Net income and comprehensive income $</t>
+          <t>General and administration (Note 14)</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -20291,26 +20301,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I227" s="5" t="n">
+        <v>0.129356</v>
+      </c>
+      <c r="J227" s="5" t="n">
+        <v>0.946261</v>
+      </c>
+      <c r="K227" s="5" t="n">
+        <v>0.7241030000000001</v>
       </c>
       <c r="L227" s="5" t="n">
-        <v>3.43796</v>
+        <v>0.847383</v>
       </c>
       <c r="M227" s="5" t="n">
-        <v>6.567281</v>
+        <v>1.009775</v>
       </c>
       <c r="N227" t="inlineStr">
         <is>
@@ -20326,17 +20330,17 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Income per common share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Basic and diluted $</t>
+          <t>Depreciation and amortization</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -20369,16 +20373,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K228" s="5" t="n">
+        <v>0.003499</v>
       </c>
       <c r="L228" s="5" t="n">
-        <v>3e-08</v>
+        <v>0.004511</v>
       </c>
       <c r="M228" s="5" t="n">
-        <v>5.999999999999999e-08</v>
+        <v>0.018243</v>
       </c>
       <c r="N228" t="inlineStr">
         <is>
@@ -20394,15 +20396,19 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr"/>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -20419,22 +20425,22 @@
         </is>
       </c>
       <c r="H229" s="5" t="n">
-        <v>36.862905</v>
+        <v>0.537045</v>
       </c>
       <c r="I229" s="5" t="n">
-        <v>40.665763</v>
+        <v>0.390527</v>
       </c>
       <c r="J229" s="5" t="n">
-        <v>97.338049</v>
+        <v>1.565153</v>
       </c>
       <c r="K229" s="5" t="n">
-        <v>112.635393</v>
+        <v>2.447864</v>
       </c>
       <c r="L229" s="5" t="n">
-        <v>112.698769</v>
+        <v>4.298846</v>
       </c>
       <c r="M229" s="5" t="n">
-        <v>112.680574</v>
+        <v>5.924257</v>
       </c>
       <c r="N229" t="inlineStr">
         <is>
@@ -20450,15 +20456,19 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Equity 20,941,357 849,745 (194,236) (19,316) 4,224 20,850 3,437,960 25,040,584 Equity 25,040,584 34,108</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr"/>
+          <t>Loss before other income</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -20484,21 +20494,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J230" s="5" t="n">
+        <v>-1.004449</v>
+      </c>
+      <c r="K230" s="5" t="n">
+        <v>-0.602653</v>
       </c>
       <c r="L230" s="5" t="n">
-        <v>31.641973</v>
+        <v>-0.018009</v>
       </c>
       <c r="M230" s="5" t="n">
-        <v>6.567281</v>
+        <v>-0.150981</v>
       </c>
       <c r="N230" t="inlineStr">
         <is>
@@ -20514,12 +20520,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Retained Earnings 3,365,906 - - - - - 3,437,960 6,803,866 Retained Earnings 6,803,866 -</t>
+          <t>Fair value adjustment on investment properties (Note 4)</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
@@ -20548,21 +20554,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J231" s="5" t="n">
+        <v>0.573039</v>
+      </c>
+      <c r="K231" s="5" t="n">
+        <v>0.6349900000000001</v>
       </c>
       <c r="L231" s="5" t="n">
-        <v>13.371147</v>
+        <v>4.161301</v>
       </c>
       <c r="M231" s="5" t="n">
-        <v>6.567281</v>
+        <v>7.947369</v>
       </c>
       <c r="N231" t="inlineStr">
         <is>
@@ -20578,15 +20580,19 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Contributed Surplus 1,509,029 - - (5,709) 4,224 (4,224) - 1,503,320 Contributed Surplus 1,503,320 34,108</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -20617,18 +20623,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K232" s="5" t="n">
+        <v>0.037108</v>
       </c>
       <c r="L232" s="5" t="n">
-        <v>1.537428</v>
-      </c>
-      <c r="M232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.018241</v>
+      </c>
+      <c r="M232" s="5" t="n">
+        <v>0.013667</v>
       </c>
       <c r="N232" t="inlineStr">
         <is>
@@ -20644,15 +20646,19 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Common Shares 17(a)) (Note 14,222,796 - - (13,607) - 25,074 - 14,234,263 Common Shares 17(a))(Note 14,234,263 -</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr"/>
+          <t>Income before income taxes</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -20683,18 +20689,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K233" s="5" t="n">
+        <v>0.06944500000000001</v>
       </c>
       <c r="L233" s="5" t="n">
-        <v>14.234263</v>
-      </c>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.161533</v>
+      </c>
+      <c r="M233" s="5" t="n">
+        <v>7.810055</v>
       </c>
       <c r="N233" t="inlineStr">
         <is>
@@ -20708,15 +20710,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr"/>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Income tax expense</t>
+        </is>
+      </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Recovery of operating expenses</t>
+          <t>Deferred income tax expense (Note 16)</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -20739,22 +20745,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I234" s="5" t="n">
-        <v>0.439969</v>
-      </c>
-      <c r="J234" s="5" t="n">
-        <v>0.415237</v>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K234" s="5" t="n">
-        <v>0.428789</v>
+        <v>-0.231418</v>
       </c>
       <c r="L234" s="5" t="n">
-        <v>0.378587</v>
-      </c>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.723573</v>
+      </c>
+      <c r="M234" s="5" t="n">
+        <v>-1.242774</v>
       </c>
       <c r="N234" t="inlineStr">
         <is>
@@ -20768,13 +20776,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr"/>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Income tax expense</t>
+        </is>
+      </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Direct operating costs</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>Net income and comprehensive income $</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -20795,22 +20811,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I235" s="5" t="n">
-        <v>-0.481142</v>
-      </c>
-      <c r="J235" s="5" t="n">
-        <v>-0.931449</v>
-      </c>
-      <c r="K235" s="5" t="n">
-        <v>-1.576912</v>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L235" s="5" t="n">
-        <v>-2.896234</v>
-      </c>
-      <c r="M235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.43796</v>
+      </c>
+      <c r="M235" s="5" t="n">
+        <v>6.567281</v>
       </c>
       <c r="N235" t="inlineStr">
         <is>
@@ -20826,15 +20846,19 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income per common share</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Bad debt</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
+          <t>Basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -20855,22 +20879,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I236" s="5" t="n">
-        <v>0.146688</v>
-      </c>
-      <c r="J236" s="5" t="n">
-        <v>0.116221</v>
-      </c>
-      <c r="K236" s="5" t="n">
-        <v>0.124982</v>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L236" s="5" t="n">
-        <v>0.068763</v>
-      </c>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3e-08</v>
+      </c>
+      <c r="M236" s="5" t="n">
+        <v>5.999999999999999e-08</v>
       </c>
       <c r="N236" t="inlineStr">
         <is>
@@ -20886,12 +20914,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Property tax</t>
+          <t>Basic and diluted</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -20911,24 +20939,22 @@
         </is>
       </c>
       <c r="H237" s="5" t="n">
-        <v>0.018148</v>
+        <v>36.862905</v>
       </c>
       <c r="I237" s="5" t="n">
-        <v>0.020459</v>
+        <v>40.665763</v>
       </c>
       <c r="J237" s="5" t="n">
-        <v>0.020937</v>
+        <v>97.338049</v>
       </c>
       <c r="K237" s="5" t="n">
-        <v>0.019231</v>
+        <v>112.635393</v>
       </c>
       <c r="L237" s="5" t="n">
-        <v>0.019396</v>
-      </c>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>112.698769</v>
+      </c>
+      <c r="M237" s="5" t="n">
+        <v>112.680574</v>
       </c>
       <c r="N237" t="inlineStr">
         <is>
@@ -20944,19 +20970,15 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Net Income (loss) and comprehensive income (loss) $</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Equity 20,941,357 849,745 (194,236) (19,316) 4,224 20,850 3,437,960 25,040,584 Equity 25,040,584 34,108</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -20987,16 +21009,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K238" s="5" t="n">
-        <v>-0.161973</v>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L238" s="5" t="n">
-        <v>3.43796</v>
-      </c>
-      <c r="M238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>31.641973</v>
+      </c>
+      <c r="M238" s="5" t="n">
+        <v>6.567281</v>
       </c>
       <c r="N238" t="inlineStr">
         <is>
@@ -21012,19 +21034,15 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Income (loss) per common share</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Retained Earnings 3,365,906 - - - - - 3,437,960 6,803,866 Retained Earnings 6,803,866 -</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -21055,16 +21073,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K239" s="5" t="n">
-        <v>0</v>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L239" s="5" t="n">
-        <v>3e-08</v>
-      </c>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>13.371147</v>
+      </c>
+      <c r="M239" s="5" t="n">
+        <v>6.567281</v>
       </c>
       <c r="N239" t="inlineStr">
         <is>
@@ -21085,7 +21103,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Equity 692,057 (121,826) 1,617 20,322 (161,973) Equity 849,745 (194,236) (19,316) 20,511,160 20,941,357 20,941,357 4,224 20,850</t>
+          <t>Contributed Surplus 1,509,029 - - (5,709) 4,224 (4,224) - 1,503,320 Contributed Surplus 1,503,320 34,108</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -21119,11 +21137,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K240" s="5" t="n">
-        <v>25.040584</v>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L240" s="5" t="n">
-        <v>3.43796</v>
+        <v>1.537428</v>
       </c>
       <c r="M240" t="inlineStr">
         <is>
@@ -21149,7 +21169,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Retained Earnings - - - - (161,973) Retained Earnings - - - - - 3,527,879 3,365,906 3,365,906</t>
+          <t>Common Shares 17(a)) (Note 14,222,796 - - (13,607) - 25,074 - 14,234,263 Common Shares 17(a))(Note 14,234,263 -</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -21183,11 +21203,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K241" s="5" t="n">
-        <v>6.803866</v>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L241" s="5" t="n">
-        <v>3.43796</v>
+        <v>14.234263</v>
       </c>
       <c r="M241" t="inlineStr">
         <is>
@@ -21206,17 +21228,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Weighted average number of common shares outstanding</t>
-        </is>
-      </c>
+      <c r="B242" t="inlineStr"/>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding total</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr"/>
+          <t>Recovery of operating expenses</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -21237,25 +21259,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I242" s="5" t="n">
+        <v>0.439969</v>
+      </c>
+      <c r="J242" s="5" t="n">
+        <v>0.415237</v>
+      </c>
+      <c r="K242" s="5" t="n">
+        <v>0.428789</v>
+      </c>
+      <c r="L242" s="5" t="n">
+        <v>0.378587</v>
       </c>
       <c r="M242" t="inlineStr">
         <is>
@@ -21274,14 +21288,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Weighted average number of common shares outstanding</t>
-        </is>
-      </c>
+      <c r="B243" t="inlineStr"/>
       <c r="C243" t="inlineStr">
         <is>
-          <t>- - 1,617 (1,617) - Surplus 17(b)) - - (5,709) 4,224 (4,224) Surplus 17(b)) Contributed (Note 1,509,029 1,509,029 Contributed (Note 1,509,029</t>
+          <t>Direct operating costs</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -21305,23 +21315,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I243" s="5" t="n">
+        <v>-0.481142</v>
+      </c>
+      <c r="J243" s="5" t="n">
+        <v>-0.931449</v>
       </c>
       <c r="K243" s="5" t="n">
-        <v>1.50332</v>
-      </c>
-      <c r="L243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.576912</v>
+      </c>
+      <c r="L243" s="5" t="n">
+        <v>-2.896234</v>
       </c>
       <c r="M243" t="inlineStr">
         <is>
@@ -21342,12 +21346,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>- (13,607) Common Shares 17(a)) - 25,074 - 14,234,263 (Note 14,200,857 - - - 21,939 - 14,222,796 Common Shares 17(a))(Note</t>
+          <t>Bad debt</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -21371,23 +21375,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I244" s="5" t="n">
+        <v>0.146688</v>
+      </c>
+      <c r="J244" s="5" t="n">
+        <v>0.116221</v>
+      </c>
+      <c r="K244" s="5" t="n">
+        <v>0.124982</v>
       </c>
       <c r="L244" s="5" t="n">
-        <v>14.222796</v>
+        <v>0.068763</v>
       </c>
       <c r="M244" t="inlineStr">
         <is>
@@ -21406,10 +21404,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr"/>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Rental revenue (Note 12) $</t>
+          <t>Property tax</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
@@ -21428,26 +21430,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I245" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H245" s="5" t="n">
+        <v>0.018148</v>
+      </c>
+      <c r="I245" s="5" t="n">
+        <v>0.020459</v>
       </c>
       <c r="J245" s="5" t="n">
-        <v>1.076916</v>
+        <v>0.020937</v>
       </c>
       <c r="K245" s="5" t="n">
-        <v>2.993334</v>
-      </c>
-      <c r="L245" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.019231</v>
+      </c>
+      <c r="L245" s="5" t="n">
+        <v>0.019396</v>
       </c>
       <c r="M245" t="inlineStr">
         <is>
@@ -21468,15 +21464,19 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income tax expense</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Financing costs (Note 14)</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr"/>
+          <t>Net Income (loss) and comprehensive income (loss) $</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -21502,16 +21502,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J246" s="5" t="n">
-        <v>0.479372</v>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K246" s="5" t="n">
-        <v>1.576049</v>
-      </c>
-      <c r="L246" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.161973</v>
+      </c>
+      <c r="L246" s="5" t="n">
+        <v>3.43796</v>
       </c>
       <c r="M246" t="inlineStr">
         <is>
@@ -21532,17 +21532,17 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income (loss) per common share</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>General and administration (Note 13)</t>
+          <t>Basic and diluted $</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -21570,16 +21570,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J247" s="5" t="n">
-        <v>0.946261</v>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K247" s="5" t="n">
-        <v>0.7241030000000001</v>
-      </c>
-      <c r="L247" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L247" s="5" t="n">
+        <v>3e-08</v>
       </c>
       <c r="M247" t="inlineStr">
         <is>
@@ -21600,19 +21600,15 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Equity 692,057 (121,826) 1,617 20,322 (161,973) Equity 849,745 (194,236) (19,316) 20,511,160 20,941,357 20,941,357 4,224 20,850</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -21628,22 +21624,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H248" s="5" t="n">
-        <v>0.002026</v>
-      </c>
-      <c r="I248" s="5" t="n">
-        <v>0.001621</v>
-      </c>
-      <c r="J248" s="5" t="n">
-        <v>0.002362</v>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K248" s="5" t="n">
-        <v>0.003499</v>
-      </c>
-      <c r="L248" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>25.040584</v>
+      </c>
+      <c r="L248" s="5" t="n">
+        <v>3.43796</v>
       </c>
       <c r="M248" t="inlineStr">
         <is>
@@ -21664,12 +21664,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Share of profit of equity-accounted investee (Note 7)</t>
+          <t>Retained Earnings - - - - (161,973) Retained Earnings - - - - - 3,527,879 3,365,906 3,365,906</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -21698,18 +21698,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J249" s="5" t="n">
-        <v>0.356703</v>
-      </c>
-      <c r="K249" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L249" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K249" s="5" t="n">
+        <v>6.803866</v>
+      </c>
+      <c r="L249" s="5" t="n">
+        <v>3.43796</v>
       </c>
       <c r="M249" t="inlineStr">
         <is>
@@ -21730,12 +21728,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Impairment of investment in Yorkton 108 LP (Note 7)</t>
+          <t>Weighted average number of common shares outstanding total</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
@@ -21764,8 +21762,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J250" s="5" t="n">
-        <v>-1.144343</v>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
@@ -21796,12 +21796,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Other income total</t>
+          <t>- - 1,617 (1,617) - Surplus 17(b)) - - (5,709) 4,224 (4,224) Surplus 17(b)) Contributed (Note 1,509,029 1,509,029 Contributed (Note 1,509,029</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
@@ -21830,11 +21830,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J251" s="5" t="n">
-        <v>-0.214601</v>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K251" s="5" t="n">
-        <v>0.672098</v>
+        <v>1.50332</v>
       </c>
       <c r="L251" t="inlineStr">
         <is>
@@ -21860,19 +21862,15 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Income (loss) before income taxes</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>- (13,607) Common Shares 17(a)) - 25,074 - 14,234,263 (Note 14,200,857 - - - 21,939 - 14,222,796 Common Shares 17(a))(Note</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -21898,16 +21896,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J252" s="5" t="n">
-        <v>-1.21905</v>
-      </c>
-      <c r="K252" s="5" t="n">
-        <v>0.06944500000000001</v>
-      </c>
-      <c r="L252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L252" s="5" t="n">
+        <v>14.222796</v>
       </c>
       <c r="M252" t="inlineStr">
         <is>
@@ -21926,14 +21926,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>Income tax recovery (expense)</t>
-        </is>
-      </c>
+      <c r="B253" t="inlineStr"/>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Current income tax recovery (Note 15)</t>
+          <t>Rental revenue (Note 12) $</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
@@ -21963,12 +21959,10 @@
         </is>
       </c>
       <c r="J253" s="5" t="n">
-        <v>0.007854</v>
-      </c>
-      <c r="K253" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.076916</v>
+      </c>
+      <c r="K253" s="5" t="n">
+        <v>2.993334</v>
       </c>
       <c r="L253" t="inlineStr">
         <is>
@@ -21994,19 +21988,15 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Income tax recovery (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Deferred income tax expense (Note 15)</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Financing costs (Note 14)</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -22033,10 +22023,10 @@
         </is>
       </c>
       <c r="J254" s="5" t="n">
-        <v>-0.04533</v>
+        <v>0.479372</v>
       </c>
       <c r="K254" s="5" t="n">
-        <v>-0.231418</v>
+        <v>1.576049</v>
       </c>
       <c r="L254" t="inlineStr">
         <is>
@@ -22062,15 +22052,19 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Income tax recovery (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Income tax recovery (expense) total</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
+          <t>General and administration (Note 13)</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -22086,17 +22080,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H255" s="5" t="n">
-        <v>0.236181</v>
-      </c>
-      <c r="I255" s="5" t="n">
-        <v>1.189673</v>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J255" s="5" t="n">
-        <v>-0.037476</v>
+        <v>0.946261</v>
       </c>
       <c r="K255" s="5" t="n">
-        <v>-0.231418</v>
+        <v>0.7241030000000001</v>
       </c>
       <c r="L255" t="inlineStr">
         <is>
@@ -22122,17 +22120,17 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Income tax recovery (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -22150,19 +22148,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H256" s="5" t="n">
+        <v>0.002026</v>
       </c>
       <c r="I256" s="5" t="n">
-        <v>-0.422355</v>
+        <v>0.001621</v>
       </c>
       <c r="J256" s="5" t="n">
-        <v>-1.256526</v>
+        <v>0.002362</v>
       </c>
       <c r="K256" s="5" t="n">
-        <v>-0.161973</v>
+        <v>0.003499</v>
       </c>
       <c r="L256" t="inlineStr">
         <is>
@@ -22188,19 +22184,15 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Income tax recovery (expense)</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Share of profit of equity-accounted investee (Note 7)</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -22221,14 +22213,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I257" s="5" t="n">
-        <v>-1e-08</v>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J257" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="K257" s="5" t="n">
-        <v>0</v>
+        <v>0.356703</v>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
@@ -22254,19 +22250,15 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Depreciation (Note 6)</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Impairment of investment in Yorkton 108 LP (Note 7)</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr"/>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
@@ -22287,11 +22279,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I258" s="5" t="n">
-        <v>0.001621</v>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J258" s="5" t="n">
-        <v>0.002362</v>
+        <v>-1.144343</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
@@ -22322,19 +22316,15 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Income (loss) before other income (expenses)</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Other income total</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr">
         <is>
           <t>-</t>
@@ -22355,16 +22345,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I259" s="5" t="n">
-        <v>0.05307</v>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J259" s="5" t="n">
-        <v>-1.004449</v>
-      </c>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.214601</v>
+      </c>
+      <c r="K259" s="5" t="n">
+        <v>0.672098</v>
       </c>
       <c r="L259" t="inlineStr">
         <is>
@@ -22390,15 +22380,19 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Listing expense (Note 4)</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr"/>
+          <t>Income (loss) before income taxes</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -22419,18 +22413,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I260" s="5" t="n">
-        <v>-0.808389</v>
-      </c>
-      <c r="J260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J260" s="5" t="n">
+        <v>-1.21905</v>
+      </c>
+      <c r="K260" s="5" t="n">
+        <v>0.06944500000000001</v>
       </c>
       <c r="L260" t="inlineStr">
         <is>
@@ -22456,15 +22448,19 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Income tax recovery (expense)</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Fair value adjustment on investment properties (Note 5)</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr"/>
+          <t>Current income tax recovery (Note 15)</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -22485,11 +22481,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I261" s="5" t="n">
-        <v>-0.8567090000000001</v>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J261" s="5" t="n">
-        <v>0.573039</v>
+        <v>0.007854</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
@@ -22520,15 +22518,19 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Income tax recovery (expense)</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Share of profit of equity-accounted investee (Note 9)</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr"/>
+          <t>Deferred income tax expense (Note 15)</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -22555,12 +22557,10 @@
         </is>
       </c>
       <c r="J262" s="5" t="n">
-        <v>0.356703</v>
-      </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.04533</v>
+      </c>
+      <c r="K262" s="5" t="n">
+        <v>-0.231418</v>
       </c>
       <c r="L262" t="inlineStr">
         <is>
@@ -22586,15 +22586,19 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Income tax recovery (expense)</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Impairment of investment in Yorkton 108 LP (Note 9)</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr"/>
+          <t>Income tax recovery (expense) total</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -22610,23 +22614,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H263" s="5" t="n">
+        <v>0.236181</v>
+      </c>
+      <c r="I263" s="5" t="n">
+        <v>1.189673</v>
       </c>
       <c r="J263" s="5" t="n">
-        <v>-1.144343</v>
-      </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.037476</v>
+      </c>
+      <c r="K263" s="5" t="n">
+        <v>-0.231418</v>
       </c>
       <c r="L263" t="inlineStr">
         <is>
@@ -22652,17 +22650,17 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Income tax recovery (expense)</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Other income (expenses) total</t>
+          <t>Net loss and comprehensive loss $</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -22680,19 +22678,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H264" s="5" t="n">
-        <v>0.029243</v>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I264" s="5" t="n">
-        <v>1.665098</v>
+        <v>-0.422355</v>
       </c>
       <c r="J264" s="5" t="n">
-        <v>0.214601</v>
-      </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.256526</v>
+      </c>
+      <c r="K264" s="5" t="n">
+        <v>-0.161973</v>
       </c>
       <c r="L264" t="inlineStr">
         <is>
@@ -22718,17 +22716,17 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Income tax recovery (expense)</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Loss before income taxes</t>
+          <t>Basic and diluted loss per common share $</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -22746,19 +22744,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H265" s="5" t="n">
-        <v>-0.027952</v>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I265" s="5" t="n">
-        <v>-1.612028</v>
+        <v>-1e-08</v>
       </c>
       <c r="J265" s="5" t="n">
-        <v>-1.21905</v>
-      </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1e-08</v>
+      </c>
+      <c r="K265" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="L265" t="inlineStr">
         <is>
@@ -22784,15 +22782,19 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Income tax recovery (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Current income tax recovery (expense) (Note 16)</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr"/>
+          <t>Depreciation (Note 6)</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
@@ -22814,10 +22816,10 @@
         </is>
       </c>
       <c r="I266" s="5" t="n">
-        <v>-0.042495</v>
+        <v>0.001621</v>
       </c>
       <c r="J266" s="5" t="n">
-        <v>0.007854</v>
+        <v>0.002362</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
@@ -22848,15 +22850,19 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Income tax recovery (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery (expense) (Note 16)</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr"/>
+          <t>Income (loss) before other income (expenses)</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -22878,10 +22884,10 @@
         </is>
       </c>
       <c r="I267" s="5" t="n">
-        <v>1.232168</v>
+        <v>0.05307</v>
       </c>
       <c r="J267" s="5" t="n">
-        <v>-0.04533</v>
+        <v>-1.004449</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
@@ -22912,12 +22918,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Rental revenue (Note 11) $</t>
+          <t>Listing expense (Note 4)</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -22936,11 +22942,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H268" s="5" t="n">
-        <v>0.562693</v>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I268" s="5" t="n">
-        <v>0.48477</v>
+        <v>-0.808389</v>
       </c>
       <c r="J268" t="inlineStr">
         <is>
@@ -22976,19 +22984,15 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Recovery of operating expenses</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Fair value adjustment on investment properties (Note 5)</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr"/>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -23004,16 +23008,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H269" s="5" t="n">
-        <v>0.470302</v>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I269" s="5" t="n">
-        <v>0.439969</v>
-      </c>
-      <c r="J269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.8567090000000001</v>
+      </c>
+      <c r="J269" s="5" t="n">
+        <v>0.573039</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
@@ -23044,12 +23048,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Common area costs</t>
+          <t>Share of profit of equity-accounted investee (Note 9)</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
@@ -23068,16 +23072,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H270" s="5" t="n">
-        <v>-0.494659</v>
-      </c>
-      <c r="I270" s="5" t="n">
-        <v>-0.481142</v>
-      </c>
-      <c r="J270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J270" s="5" t="n">
+        <v>0.356703</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
@@ -23108,19 +23114,15 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Revenues total</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Impairment of investment in Yorkton 108 LP (Note 9)</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
@@ -23136,16 +23138,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H271" s="5" t="n">
-        <v>0.538336</v>
-      </c>
-      <c r="I271" s="5" t="n">
-        <v>0.443597</v>
-      </c>
-      <c r="J271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J271" s="5" t="n">
+        <v>-1.144343</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
@@ -23176,17 +23180,17 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>General and administration</t>
+          <t>Other income (expenses) total</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -23205,15 +23209,13 @@
         </is>
       </c>
       <c r="H272" s="5" t="n">
-        <v>0.020089</v>
+        <v>0.029243</v>
       </c>
       <c r="I272" s="5" t="n">
-        <v>0.129356</v>
-      </c>
-      <c r="J272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.665098</v>
+      </c>
+      <c r="J272" s="5" t="n">
+        <v>0.214601</v>
       </c>
       <c r="K272" t="inlineStr">
         <is>
@@ -23244,15 +23246,19 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Interest</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr"/>
+          <t>Loss before income taxes</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -23269,15 +23275,13 @@
         </is>
       </c>
       <c r="H273" s="5" t="n">
-        <v>0.116782</v>
+        <v>-0.027952</v>
       </c>
       <c r="I273" s="5" t="n">
-        <v>0.092403</v>
-      </c>
-      <c r="J273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.612028</v>
+      </c>
+      <c r="J273" s="5" t="n">
+        <v>-1.21905</v>
       </c>
       <c r="K273" t="inlineStr">
         <is>
@@ -23308,17 +23312,17 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income tax recovery (expense)</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Management fees (Note 8)</t>
+          <t>Current income tax recovery (expense) (Note 16)</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -23336,18 +23340,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H274" s="5" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="I274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I274" s="5" t="n">
+        <v>-0.042495</v>
+      </c>
+      <c r="J274" s="5" t="n">
+        <v>0.007854</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
@@ -23378,15 +23380,19 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income tax recovery (expense)</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Income before other income (expenses)</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr"/>
+          <t>Deferred income tax recovery (expense) (Note 16)</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -23402,16 +23408,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H275" s="5" t="n">
-        <v>0.001291</v>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I275" s="5" t="n">
-        <v>0.05307</v>
-      </c>
-      <c r="J275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.232168</v>
+      </c>
+      <c r="J275" s="5" t="n">
+        <v>-0.04533</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
@@ -23442,12 +23448,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Fair value adjustment on investment property (Note 5)</t>
+          <t>Rental revenue (Note 11) $</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
@@ -23467,10 +23473,10 @@
         </is>
       </c>
       <c r="H276" s="5" t="n">
-        <v>-0.029243</v>
+        <v>0.562693</v>
       </c>
       <c r="I276" s="5" t="n">
-        <v>-0.8567090000000001</v>
+        <v>0.48477</v>
       </c>
       <c r="J276" t="inlineStr">
         <is>
@@ -23506,17 +23512,17 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Income tax recovery (expense)</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Current income tax expense (Note 12)</t>
+          <t>Recovery of operating expenses</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -23534,13 +23540,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H277" s="5" t="n">
+        <v>0.470302</v>
       </c>
       <c r="I277" s="5" t="n">
-        <v>-0.042495</v>
+        <v>0.439969</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
@@ -23576,12 +23580,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Income tax recovery (expense)</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Deferred income taxes recovery (Note 12)</t>
+          <t>Common area costs</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
@@ -23601,10 +23605,10 @@
         </is>
       </c>
       <c r="H278" s="5" t="n">
-        <v>0.236181</v>
+        <v>-0.494659</v>
       </c>
       <c r="I278" s="5" t="n">
-        <v>1.232168</v>
+        <v>-0.481142</v>
       </c>
       <c r="J278" t="inlineStr">
         <is>
@@ -23640,15 +23644,19 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Income tax recovery (expense)</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Net (loss) income and comprehensive (loss) income $</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr"/>
+          <t>Revenues total</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>
@@ -23665,10 +23673,10 @@
         </is>
       </c>
       <c r="H279" s="5" t="n">
-        <v>0.208229</v>
+        <v>0.538336</v>
       </c>
       <c r="I279" s="5" t="n">
-        <v>-0.422355</v>
+        <v>0.443597</v>
       </c>
       <c r="J279" t="inlineStr">
         <is>
@@ -23704,15 +23712,19 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Income tax recovery (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Basic and diluted (loss) income per common share $</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
+          <t>General and administration</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -23729,10 +23741,10 @@
         </is>
       </c>
       <c r="H280" s="5" t="n">
-        <v>1e-08</v>
+        <v>0.020089</v>
       </c>
       <c r="I280" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.129356</v>
       </c>
       <c r="J280" t="inlineStr">
         <is>
@@ -23773,32 +23785,30 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Professional fees $</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F281" s="5" t="n">
-        <v>0.071149</v>
-      </c>
-      <c r="G281" s="5" t="n">
-        <v>0.06447799999999999</v>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H281" s="5" t="n">
-        <v>0.114533</v>
-      </c>
-      <c r="I281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.116782</v>
+      </c>
+      <c r="I281" s="5" t="n">
+        <v>0.092403</v>
       </c>
       <c r="J281" t="inlineStr">
         <is>
@@ -23839,23 +23849,31 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Finance costs $</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr"/>
+          <t>Management fees (Note 8)</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F282" s="5" t="n">
-        <v>2.3e-05</v>
-      </c>
-      <c r="G282" s="5" t="n">
-        <v>0.000128</v>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H282" s="5" t="n">
-        <v>0.000159</v>
+        <v>0.38</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
@@ -23901,32 +23919,30 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>General and administrative expenses $</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Income before other income (expenses)</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F283" s="5" t="n">
-        <v>0.014724</v>
-      </c>
-      <c r="G283" s="5" t="n">
-        <v>8.2e-05</v>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H283" s="5" t="n">
-        <v>0.003173</v>
-      </c>
-      <c r="I283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.001291</v>
+      </c>
+      <c r="I283" s="5" t="n">
+        <v>0.05307</v>
       </c>
       <c r="J283" t="inlineStr">
         <is>
@@ -23962,12 +23978,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Regulatory and filing fees (Note 10) $</t>
+          <t>Fair value adjustment on investment property (Note 5)</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
@@ -23981,16 +23997,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G284" s="5" t="n">
-        <v>-0.01492</v>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H284" s="5" t="n">
-        <v>0.00546</v>
-      </c>
-      <c r="I284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.029243</v>
+      </c>
+      <c r="I284" s="5" t="n">
+        <v>-0.8567090000000001</v>
       </c>
       <c r="J284" t="inlineStr">
         <is>
@@ -24026,35 +24042,41 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income tax recovery (expense)</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Total expenses $</t>
+          <t>Current income tax expense (Note 12)</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E285" s="5" t="n">
-        <v>0.202003</v>
-      </c>
-      <c r="F285" s="5" t="n">
-        <v>0.126543</v>
-      </c>
-      <c r="G285" s="5" t="n">
-        <v>0.049768</v>
-      </c>
-      <c r="H285" s="5" t="n">
-        <v>0.123325</v>
-      </c>
-      <c r="I285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I285" s="5" t="n">
+        <v>-0.042495</v>
       </c>
       <c r="J285" t="inlineStr">
         <is>
@@ -24090,35 +24112,35 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income tax recovery (expense)</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E286" s="5" t="n">
-        <v>-0.202003</v>
-      </c>
-      <c r="F286" s="5" t="n">
-        <v>-0.101543</v>
-      </c>
-      <c r="G286" s="5" t="n">
-        <v>-0.049768</v>
+          <t>Deferred income taxes recovery (Note 12)</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr"/>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H286" s="5" t="n">
-        <v>-0.123325</v>
-      </c>
-      <c r="I286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.236181</v>
+      </c>
+      <c r="I286" s="5" t="n">
+        <v>1.232168</v>
       </c>
       <c r="J286" t="inlineStr">
         <is>
@@ -24154,37 +24176,35 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income tax recovery (expense)</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Net (loss) income and comprehensive (loss) income $</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F287" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="G287" s="5" t="n">
-        <v>-2e-08</v>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H287" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
-      </c>
-      <c r="I287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.208229</v>
+      </c>
+      <c r="I287" s="5" t="n">
+        <v>-0.422355</v>
       </c>
       <c r="J287" t="inlineStr">
         <is>
@@ -24220,12 +24240,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income tax recovery (expense)</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Weighted average common shares outstanding – basic and diluted (Note 5)</t>
+          <t>Basic and diluted (loss) income per common share $</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -24234,19 +24254,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F288" s="5" t="n">
-        <v>2.1437</v>
-      </c>
-      <c r="G288" s="5" t="n">
-        <v>2.1437</v>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H288" s="5" t="n">
-        <v>2.1437</v>
-      </c>
-      <c r="I288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1e-08</v>
+      </c>
+      <c r="I288" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="J288" t="inlineStr">
         <is>
@@ -24282,28 +24304,32 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>($)               ($)           ($)                  ($)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>As at December 31, 2017 3,962,900 557,986 118,557</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr"/>
+          <t>Professional fees $</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F289" s="5" t="n">
-        <v>0.372997</v>
+        <v>0.071149</v>
       </c>
       <c r="G289" s="5" t="n">
-        <v>0.372997</v>
+        <v>0.06447799999999999</v>
       </c>
       <c r="H289" s="5" t="n">
-        <v>-0.303546</v>
+        <v>0.114533</v>
       </c>
       <c r="I289" t="inlineStr">
         <is>
@@ -24344,34 +24370,28 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>($)               ($)           ($)                  ($)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss - - -</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Finance costs $</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F290" s="5" t="n">
+        <v>2.3e-05</v>
       </c>
       <c r="G290" s="5" t="n">
-        <v>-0.049768</v>
+        <v>0.000128</v>
       </c>
       <c r="H290" s="5" t="n">
-        <v>-0.049768</v>
+        <v>0.000159</v>
       </c>
       <c r="I290" t="inlineStr">
         <is>
@@ -24412,28 +24432,32 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>($)               ($)           ($)                  ($)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>As at December 31, 2018 3,962,900 557,986 118,557</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr"/>
+          <t>General and administrative expenses $</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F291" s="5" t="n">
-        <v>0.323229</v>
+        <v>0.014724</v>
       </c>
       <c r="G291" s="5" t="n">
-        <v>0.323229</v>
+        <v>8.2e-05</v>
       </c>
       <c r="H291" s="5" t="n">
-        <v>-0.353314</v>
+        <v>0.003173</v>
       </c>
       <c r="I291" t="inlineStr">
         <is>
@@ -24474,12 +24498,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>($)               ($)           ($)                  ($)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>As at December 31, 2019 3,962,900 557,986 118,557</t>
+          <t>Regulatory and filing fees (Note 10) $</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -24494,10 +24518,10 @@
         </is>
       </c>
       <c r="G292" s="5" t="n">
-        <v>0.199904</v>
+        <v>-0.01492</v>
       </c>
       <c r="H292" s="5" t="n">
-        <v>-0.476639</v>
+        <v>0.00546</v>
       </c>
       <c r="I292" t="inlineStr">
         <is>
@@ -24536,30 +24560,32 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B293" t="inlineStr"/>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Termination fee (note 11) $</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr"/>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total expenses $</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E293" s="5" t="n">
+        <v>0.202003</v>
       </c>
       <c r="F293" s="5" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="G293" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H293" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.126543</v>
+      </c>
+      <c r="G293" s="5" t="n">
+        <v>0.049768</v>
+      </c>
+      <c r="H293" s="5" t="n">
+        <v>0.123325</v>
       </c>
       <c r="I293" t="inlineStr">
         <is>
@@ -24605,25 +24631,25 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Regulatory and filing fees (note 11) $</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr"/>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E294" s="5" t="n">
+        <v>-0.202003</v>
       </c>
       <c r="F294" s="5" t="n">
-        <v>0.040647</v>
+        <v>-0.101543</v>
       </c>
       <c r="G294" s="5" t="n">
-        <v>-0.01492</v>
-      </c>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.049768</v>
+      </c>
+      <c r="H294" s="5" t="n">
+        <v>-0.123325</v>
       </c>
       <c r="I294" t="inlineStr">
         <is>
@@ -24664,30 +24690,32 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>($)               ($)           ($)                  ($)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>As at January 1, 2017 3,962,900 557,986 118,557</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr"/>
+          <t>Basic and diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F295" s="5" t="n">
-        <v>0.47454</v>
+        <v>-3e-08</v>
       </c>
       <c r="G295" s="5" t="n">
-        <v>-0.202003</v>
-      </c>
-      <c r="H295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2e-08</v>
+      </c>
+      <c r="H295" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
       </c>
       <c r="I295" t="inlineStr">
         <is>
@@ -24728,34 +24756,28 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>($)               ($)           ($)                  ($)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss - - -</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Weighted average common shares outstanding – basic and diluted (Note 5)</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F296" s="5" t="n">
-        <v>-0.101543</v>
+        <v>2.1437</v>
       </c>
       <c r="G296" s="5" t="n">
-        <v>-0.101543</v>
-      </c>
-      <c r="H296" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.1437</v>
+      </c>
+      <c r="H296" s="5" t="n">
+        <v>2.1437</v>
       </c>
       <c r="I296" t="inlineStr">
         <is>
@@ -24796,32 +24818,28 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>($)               ($)           ($)                  ($)</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Regulatory and filing fees $</t>
+          <t>As at December 31, 2017 3,962,900 557,986 118,557</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
-      <c r="E297" s="5" t="n">
-        <v>0.01639</v>
-      </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F297" s="5" t="n">
+        <v>0.372997</v>
+      </c>
+      <c r="G297" s="5" t="n">
+        <v>0.372997</v>
+      </c>
+      <c r="H297" s="5" t="n">
+        <v>-0.303546</v>
       </c>
       <c r="I297" t="inlineStr">
         <is>
@@ -24862,36 +24880,34 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>($)               ($)           ($)                  ($)</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Loss and comprehensive loss - - -</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E298" s="5" t="n">
-        <v>0.002604</v>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G298" s="5" t="n">
+        <v>-0.049768</v>
+      </c>
+      <c r="H298" s="5" t="n">
+        <v>-0.049768</v>
       </c>
       <c r="I298" t="inlineStr">
         <is>
@@ -24932,36 +24948,28 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>($)               ($)           ($)                  ($)</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E299" s="5" t="n">
-        <v>0.09435</v>
-      </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>As at December 31, 2018 3,962,900 557,986 118,557</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F299" s="5" t="n">
+        <v>0.323229</v>
+      </c>
+      <c r="G299" s="5" t="n">
+        <v>0.323229</v>
+      </c>
+      <c r="H299" s="5" t="n">
+        <v>-0.353314</v>
       </c>
       <c r="I299" t="inlineStr">
         <is>
@@ -25002,32 +25010,30 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>($)               ($)           ($)                  ($)</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 6)</t>
+          <t>As at December 31, 2019 3,962,900 557,986 118,557</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
-      <c r="E300" s="5" t="n">
-        <v>0.088659</v>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H300" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G300" s="5" t="n">
+        <v>0.199904</v>
+      </c>
+      <c r="H300" s="5" t="n">
+        <v>-0.476639</v>
       </c>
       <c r="I300" t="inlineStr">
         <is>
@@ -25066,24 +25072,20 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B301" t="inlineStr"/>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Basic loss per share (Note 6) $</t>
+          <t>Termination fee (note 11) $</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
-      <c r="E301" s="5" t="n">
-        <v>-1.04e-06</v>
-      </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F301" s="5" t="n">
+        <v>0.025</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
@@ -25134,31 +25136,25 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Weighted average common shares</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Weighted average common shares outstanding (Note 6)</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
-      <c r="E302" s="5" t="n">
-        <v>0.19389</v>
-      </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Regulatory and filing fees (note 11) $</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F302" s="5" t="n">
+        <v>0.040647</v>
+      </c>
+      <c r="G302" s="5" t="n">
+        <v>-0.01492</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
@@ -25209,7 +25205,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>As at March 4, 2016 - - - -</t>
+          <t>As at January 1, 2017 3,962,900 557,986 118,557</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -25218,15 +25214,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F303" s="5" t="n">
+        <v>0.47454</v>
+      </c>
+      <c r="G303" s="5" t="n">
+        <v>-0.202003</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>
@@ -25277,22 +25269,24 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Share issuance (Note 6) 3,962,900 780,725 - -</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr"/>
-      <c r="E304" s="5" t="n">
-        <v>0.780725</v>
-      </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss and comprehensive loss - - -</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F304" s="5" t="n">
+        <v>-0.101543</v>
+      </c>
+      <c r="G304" s="5" t="n">
+        <v>-0.101543</v>
       </c>
       <c r="H304" t="inlineStr">
         <is>
@@ -25338,17 +25332,17 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>($)               ($)           ($)                  ($)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Share issuance costs (Note 6) - (222,739) - -</t>
+          <t>Regulatory and filing fees $</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
       <c r="E305" s="5" t="n">
-        <v>-0.222739</v>
+        <v>0.01639</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25404,17 +25398,21 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>($)               ($)           ($)                  ($)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Options issued (Note 6) - - 118,557 -</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr"/>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E306" s="5" t="n">
-        <v>0.118557</v>
+        <v>0.002604</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25470,17 +25468,21 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>($)               ($)           ($)                  ($)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss - - - (202,003)</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E307" s="5" t="n">
-        <v>-0.202003</v>
+        <v>0.09435</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25536,59 +25538,593 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>($)               ($)           ($)                  ($)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>As at December 31, 2016 3,962,900 557,986 118,557 (202,003)</t>
+          <t>Share-based compensation (Note 6)</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
       <c r="E308" s="5" t="n">
+        <v>0.088659</v>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Basic loss per share (Note 6) $</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr"/>
+      <c r="E309" s="5" t="n">
+        <v>-1.04e-06</v>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Weighted average common shares</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Weighted average common shares outstanding (Note 6)</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E310" s="5" t="n">
+        <v>0.19389</v>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>($)               ($)           ($)                  ($)</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>As at March 4, 2016 - - - -</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>($)               ($)           ($)                  ($)</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Share issuance (Note 6) 3,962,900 780,725 - -</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
+      <c r="E312" s="5" t="n">
+        <v>0.780725</v>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>($)               ($)           ($)                  ($)</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Share issuance costs (Note 6) - (222,739) - -</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr"/>
+      <c r="E313" s="5" t="n">
+        <v>-0.222739</v>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>($)               ($)           ($)                  ($)</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Options issued (Note 6) - - 118,557 -</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
+      <c r="E314" s="5" t="n">
+        <v>0.118557</v>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>($)               ($)           ($)                  ($)</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss - - - (202,003)</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
+      <c r="E315" s="5" t="n">
+        <v>-0.202003</v>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>($)               ($)           ($)                  ($)</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>As at December 31, 2016 3,962,900 557,986 118,557 (202,003)</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
+      <c r="E316" s="5" t="n">
         <v>0.47454</v>
       </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N308" t="inlineStr">
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr">
         <is>
           <t>-</t>
         </is>
